--- a/data/trans_camb/P1423-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1423-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,88</t>
+          <t>-1,38; 2,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,47</t>
+          <t>-1,6; 2,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 4,71</t>
+          <t>0,15; 4,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 3,66</t>
+          <t>-3,81; 2,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,56</t>
+          <t>-3,7; 3,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 6,03</t>
+          <t>-0,67; 5,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,36</t>
+          <t>-1,77; 2,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,17</t>
+          <t>-1,77; 2,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,6</t>
+          <t>0,83; 4,69</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,11; 233,29</t>
+          <t>-47,72; 225,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,28; 164,51</t>
+          <t>-53,91; 169,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 323,47</t>
+          <t>-7,09; 327,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,77; 112,43</t>
+          <t>-61,22; 93,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,83; 105,66</t>
+          <t>-56,71; 89,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 194,02</t>
+          <t>-10,7; 181,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 97,72</t>
+          <t>-43,0; 88,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 86,44</t>
+          <t>-42,28; 89,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 183,89</t>
+          <t>15,89; 191,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,68</t>
+          <t>-1,37; 3,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,07</t>
+          <t>-2,08; 2,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,19</t>
+          <t>0,95; 6,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 3,15</t>
+          <t>-3,61; 2,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,51</t>
+          <t>-5,01; 1,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 8,01</t>
+          <t>0,56; 7,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,39</t>
+          <t>-2,15; 2,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,22</t>
+          <t>-2,73; 1,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,01</t>
+          <t>1,41; 5,95</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,29; 289,37</t>
+          <t>-48,88; 369,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,06; 169,24</t>
+          <t>-66,88; 236,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,44; 558,36</t>
+          <t>20,96; 565,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,69; 76,47</t>
+          <t>-50,92; 66,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,31; 39,46</t>
+          <t>-64,55; 46,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 182,06</t>
+          <t>6,05; 185,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,51; 85,16</t>
+          <t>-42,14; 79,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,01; 41,4</t>
+          <t>-52,67; 49,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,57; 209,39</t>
+          <t>24,78; 202,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,82</t>
+          <t>0,4; 5,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,79</t>
+          <t>-2,08; 2,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,88</t>
+          <t>-3,16; 5,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 10,18</t>
+          <t>-2,96; 10,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 10,26</t>
+          <t>-4,39; 11,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 9,0</t>
+          <t>-4,06; 9,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,45</t>
+          <t>1,18; 6,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,38</t>
+          <t>-1,5; 3,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 4,71</t>
+          <t>-3,69; 4,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 223,16</t>
+          <t>2,36; 228,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 104,5</t>
+          <t>-41,19; 110,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,31; 148,03</t>
+          <t>-58,29; 155,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 140,62</t>
+          <t>-21,38; 160,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 140,91</t>
+          <t>-34,11; 161,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 121,42</t>
+          <t>-29,08; 128,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,7; 153,68</t>
+          <t>17,36; 160,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 82,09</t>
+          <t>-23,86; 84,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,75; 94,36</t>
+          <t>-55,12; 97,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,35</t>
+          <t>-0,23; 3,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,91</t>
+          <t>-1,15; 1,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,66</t>
+          <t>1,07; 4,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 6,13</t>
+          <t>-0,39; 5,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,39</t>
+          <t>-2,43; 3,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 4,67</t>
+          <t>-3,77; 4,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,81</t>
+          <t>0,69; 3,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,07</t>
+          <t>-0,76; 2,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,2</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 129,4</t>
+          <t>-6,91; 128,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,12; 72,68</t>
+          <t>-31,13; 74,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,74; 182,8</t>
+          <t>25,22; 166,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 90,92</t>
+          <t>-5,34; 85,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 50,37</t>
+          <t>-25,97; 48,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,99; 65,11</t>
+          <t>-39,15; 62,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,96; 84,81</t>
+          <t>11,06; 88,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 48,44</t>
+          <t>-13,92; 48,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 92,92</t>
+          <t>0,56; 90,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 1,1</t>
+          <t>-4,44; 1,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,16</t>
+          <t>-3,51; 1,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 6,37</t>
+          <t>-0,43; 6,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 9,37</t>
+          <t>2,05; 9,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 9,92</t>
+          <t>2,27; 9,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,12</t>
+          <t>1,3; 9,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,11</t>
+          <t>0,09; 5,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,05</t>
+          <t>0,11; 4,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,1</t>
+          <t>1,66; 7,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 41,45</t>
+          <t>-64,8; 47,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 77,95</t>
+          <t>-54,44; 63,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 225,72</t>
+          <t>-8,83; 194,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18,76; 128,45</t>
+          <t>18,97; 118,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,59; 140,1</t>
+          <t>20,43; 128,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,35; 121,04</t>
+          <t>13,71; 130,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,1; 82,49</t>
+          <t>-0,01; 85,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,23; 83,47</t>
+          <t>1,21; 78,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>20,6; 110,48</t>
+          <t>21,78; 121,24</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,08</t>
+          <t>-4,42; -0,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,14</t>
+          <t>-3,42; 1,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 9,5</t>
+          <t>-0,24; 9,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,44</t>
+          <t>2,67; 7,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,57</t>
+          <t>1,69; 6,71</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,69</t>
+          <t>2,63; 7,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,74</t>
+          <t>1,56; 5,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,03</t>
+          <t>0,78; 4,96</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,41</t>
+          <t>2,2; 6,81</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,81</t>
+          <t>-100,0; 17,4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-90,09; 120,64</t>
+          <t>-88,81; 139,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 623,51</t>
+          <t>-25,95; 704,34</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29,98; 117,75</t>
+          <t>29,22; 118,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17,58; 105,08</t>
+          <t>20,6; 110,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,23; 122,72</t>
+          <t>30,45; 119,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,26; 105,22</t>
+          <t>20,41; 107,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14,14; 93,6</t>
+          <t>10,55; 93,29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28,48; 114,03</t>
+          <t>29,62; 120,85</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,86</t>
+          <t>-0,03; 1,89</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,01</t>
+          <t>-0,64; 0,98</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,6</t>
+          <t>1,22; 3,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,3</t>
+          <t>2,43; 5,12</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,08</t>
+          <t>1,23; 4,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,32</t>
+          <t>1,3; 5,15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,3</t>
+          <t>1,59; 3,32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,33</t>
+          <t>0,62; 2,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,21</t>
+          <t>1,95; 4,15</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 68,06</t>
+          <t>-1,45; 67,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 37,69</t>
+          <t>-18,45; 34,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31,06; 132,7</t>
+          <t>36,78; 132,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29,7; 76,18</t>
+          <t>29,42; 73,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>13,65; 59,0</t>
+          <t>15,01; 58,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,89; 75,72</t>
+          <t>16,9; 73,66</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,94; 66,05</t>
+          <t>27,72; 66,83</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>10,98; 46,22</t>
+          <t>10,71; 45,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33,68; 83,09</t>
+          <t>35,17; 82,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1423-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1423-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,74</t>
         </is>
       </c>
     </row>
@@ -677,42 +677,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,9</t>
+          <t>-1,54; 2,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,41</t>
+          <t>-1,67; 2,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,78</t>
+          <t>-0,1; 4,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,89</t>
+          <t>-3,64; 3,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,06</t>
+          <t>-3,77; 3,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,9</t>
+          <t>-0,83; 6,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,18</t>
+          <t>-1,59; 2,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,18</t>
+          <t>-1,46; 2,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102,54%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,72; 225,85</t>
+          <t>-51,85; 209,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,91; 169,15</t>
+          <t>-56,76; 183,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 327,0</t>
+          <t>-10,18; 307,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,22; 93,37</t>
+          <t>-55,21; 110,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 89,33</t>
+          <t>-56,23; 100,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 181,01</t>
+          <t>-13,1; 196,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 88,96</t>
+          <t>-39,05; 92,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,28; 89,07</t>
+          <t>-35,53; 93,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,89; 191,67</t>
+          <t>17,17; 189,82</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>3,98</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,61</t>
+          <t>-1,29; 3,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,43</t>
+          <t>-2,18; 2,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,42</t>
+          <t>0,94; 6,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,93</t>
+          <t>-3,94; 3,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,61</t>
+          <t>-5,01; 1,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,82</t>
+          <t>0,66; 7,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,32</t>
+          <t>-2,13; 2,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,36</t>
+          <t>-2,76; 1,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,95</t>
+          <t>1,35; 6,06</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161,78%</t>
+          <t>168,1%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 369,4</t>
+          <t>-47,13; 283,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,88; 236,51</t>
+          <t>-73,45; 189,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,96; 565,45</t>
+          <t>6,77; 513,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 66,13</t>
+          <t>-52,83; 75,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,55; 46,37</t>
+          <t>-67,04; 40,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 185,97</t>
+          <t>7,28; 189,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,14; 79,5</t>
+          <t>-40,32; 76,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,67; 49,3</t>
+          <t>-53,22; 41,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,78; 202,71</t>
+          <t>24,89; 201,02</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>3,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,83</t>
+          <t>0,43; 5,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,81</t>
+          <t>-1,93; 2,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 5,07</t>
+          <t>0,91; 6,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 10,49</t>
+          <t>-2,35; 10,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 11,02</t>
+          <t>-4,08; 11,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 9,34</t>
+          <t>-4,07; 8,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,55</t>
+          <t>1,05; 6,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,61</t>
+          <t>-1,33; 3,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 4,77</t>
+          <t>0,83; 6,28</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,36; 228,4</t>
+          <t>3,44; 229,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,19; 110,43</t>
+          <t>-42,72; 115,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,29; 155,97</t>
+          <t>14,08; 267,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 160,35</t>
+          <t>-18,68; 165,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 161,29</t>
+          <t>-34,39; 151,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 128,46</t>
+          <t>-29,74; 136,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,36; 160,45</t>
+          <t>15,22; 157,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 84,1</t>
+          <t>-21,5; 99,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,12; 97,28</t>
+          <t>12,9; 159,71</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>3,58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>3,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,17</t>
+          <t>-0,0; 3,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,81</t>
+          <t>-1,11; 1,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,43</t>
+          <t>1,3; 4,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,82</t>
+          <t>-0,13; 5,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 3,29</t>
+          <t>-2,11; 3,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,43</t>
+          <t>0,57; 6,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,74</t>
+          <t>0,72; 3,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,13</t>
+          <t>-0,77; 2,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>1,98; 4,99</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 128,9</t>
+          <t>-0,88; 130,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 74,6</t>
+          <t>-30,91; 70,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,22; 166,65</t>
+          <t>30,84; 179,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 85,39</t>
+          <t>-1,82; 87,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 48,77</t>
+          <t>-22,3; 48,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 62,18</t>
+          <t>5,35; 95,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,06; 88,07</t>
+          <t>12,65; 87,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 48,68</t>
+          <t>-13,95; 49,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 90,79</t>
+          <t>33,57; 116,28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>5,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 1,32</t>
+          <t>-4,48; 1,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,93</t>
+          <t>-3,53; 1,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 6,34</t>
+          <t>-1,34; 5,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 9,0</t>
+          <t>1,85; 9,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,44</t>
+          <t>2,35; 9,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 9,58</t>
+          <t>4,22; 10,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,24</t>
+          <t>0,31; 5,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,92</t>
+          <t>0,19; 4,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,45</t>
+          <t>2,86; 7,33</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,8; 47,12</t>
+          <t>-67,18; 42,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,44; 63,88</t>
+          <t>-51,52; 66,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 194,38</t>
+          <t>-21,62; 161,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18,97; 118,71</t>
+          <t>15,56; 121,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,43; 128,27</t>
+          <t>20,96; 118,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,71; 130,8</t>
+          <t>36,51; 141,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 85,72</t>
+          <t>4,32; 83,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,21; 78,17</t>
+          <t>2,2; 74,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21,78; 121,24</t>
+          <t>31,3; 117,99</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,38</t>
+          <t>4,59</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -0,1</t>
+          <t>-4,08; 0,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,2</t>
+          <t>-3,56; 0,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 9,5</t>
+          <t>0,12; 9,43</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,43</t>
+          <t>2,76; 7,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,71</t>
+          <t>1,75; 6,48</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,67</t>
+          <t>2,52; 7,56</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,79</t>
+          <t>1,67; 5,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,96</t>
+          <t>0,98; 5,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,81</t>
+          <t>2,55; 7,1</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127,63%</t>
+          <t>163,58%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>72,42%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 17,4</t>
+          <t>-100,0; 80,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-88,81; 139,43</t>
+          <t>-89,75; 142,55</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 704,34</t>
+          <t>-21,06; 608,93</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29,22; 118,02</t>
+          <t>32,98; 121,87</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>20,6; 110,47</t>
+          <t>20,72; 101,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,45; 119,06</t>
+          <t>30,2; 119,14</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,41; 107,03</t>
+          <t>22,89; 102,9</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10,55; 93,29</t>
+          <t>13,09; 93,15</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29,62; 120,85</t>
+          <t>33,85; 131,33</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,75</t>
+          <t>4,74</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>3,9</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,89</t>
+          <t>0,13; 2,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,98</t>
+          <t>-0,68; 0,97</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,64</t>
+          <t>1,9; 4,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,12</t>
+          <t>2,51; 5,31</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,1</t>
+          <t>1,29; 3,98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,15</t>
+          <t>3,54; 6,05</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,32</t>
+          <t>1,62; 3,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,25</t>
+          <t>0,61; 2,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,15</t>
+          <t>2,98; 4,7</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>72,53%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 67,88</t>
+          <t>3,42; 74,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 34,84</t>
+          <t>-19,63; 35,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36,78; 132,41</t>
+          <t>51,88; 150,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29,42; 73,11</t>
+          <t>30,72; 77,45</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,01; 58,93</t>
+          <t>15,61; 57,61</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,9; 73,66</t>
+          <t>43,04; 88,97</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,72; 66,83</t>
+          <t>27,82; 65,67</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>10,71; 45,45</t>
+          <t>10,73; 44,72</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>35,17; 82,45</t>
+          <t>52,36; 94,71</t>
         </is>
       </c>
     </row>
